--- a/Data/acteur.xlsx
+++ b/Data/acteur.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Documents\Sem3\SAE\BDD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trann\Documents\IUT\sem 3\SAE\BDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFADBABD-3445-4D5B-9AAF-554B2B1741C0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFF2714-33E3-45E8-A491-9230BE8E23F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="acteur" sheetId="1" r:id="rId1"/>
@@ -3326,11 +3326,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3349,9 +3350,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3389,9 +3390,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3424,26 +3425,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3476,26 +3460,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3670,22 +3637,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E702"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="3" max="3" width="22" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1087</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
@@ -3695,7 +3662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3712,7 +3679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3729,7 +3696,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3746,7 +3713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3763,7 +3730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3780,7 +3747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3797,7 +3764,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3814,7 +3781,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3831,7 +3798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3848,7 +3815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3865,7 +3832,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3882,7 +3849,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3899,7 +3866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3916,7 +3883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3933,7 +3900,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3950,7 +3917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3967,7 +3934,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3984,7 +3951,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4001,7 +3968,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4018,7 +3985,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4035,7 +4002,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4052,7 +4019,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4069,7 +4036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4086,7 +4053,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4103,7 +4070,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4120,7 +4087,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4137,7 +4104,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4154,7 +4121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4171,7 +4138,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4188,7 +4155,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4205,7 +4172,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4222,7 +4189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4239,7 +4206,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4256,7 +4223,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4273,7 +4240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4290,7 +4257,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4307,7 +4274,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4324,7 +4291,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4341,7 +4308,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4358,7 +4325,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4375,7 +4342,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4392,7 +4359,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4409,7 +4376,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4426,7 +4393,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4443,7 +4410,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4460,7 +4427,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4477,7 +4444,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4494,7 +4461,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4511,7 +4478,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4528,7 +4495,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4545,7 +4512,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4562,7 +4529,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4576,7 +4543,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4593,7 +4560,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4610,7 +4577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4627,7 +4594,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4644,7 +4611,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4661,7 +4628,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4678,7 +4645,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4695,7 +4662,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4712,7 +4679,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -4726,7 +4693,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -4743,7 +4710,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -4757,7 +4724,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -4774,7 +4741,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -4791,7 +4758,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -4808,7 +4775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -4825,7 +4792,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -4842,7 +4809,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4859,7 +4826,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4876,7 +4843,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4893,7 +4860,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4910,7 +4877,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4927,7 +4894,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4944,7 +4911,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4961,7 +4928,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4978,7 +4945,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4995,7 +4962,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -5012,7 +4979,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -5029,7 +4996,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -5046,7 +5013,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -5063,7 +5030,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -5077,7 +5044,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -5091,7 +5058,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -5108,7 +5075,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -5125,7 +5092,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -5139,7 +5106,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -5156,7 +5123,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -5173,7 +5140,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5190,7 +5157,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5207,7 +5174,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5224,7 +5191,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5241,7 +5208,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5258,7 +5225,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5275,7 +5242,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5292,7 +5259,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5309,7 +5276,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5326,7 +5293,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5343,7 +5310,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5360,7 +5327,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5377,7 +5344,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5394,7 +5361,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5408,7 +5375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5425,7 +5392,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5439,7 +5406,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5456,7 +5423,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5473,7 +5440,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5487,7 +5454,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5504,7 +5471,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5521,7 +5488,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5538,7 +5505,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5555,7 +5522,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5569,7 +5536,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5583,7 +5550,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5597,7 +5564,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5611,7 +5578,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5628,7 +5595,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5642,7 +5609,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5659,7 +5626,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5676,7 +5643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5693,7 +5660,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5710,7 +5677,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5727,7 +5694,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5744,7 +5711,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5761,7 +5728,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -5778,7 +5745,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -5795,7 +5762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -5812,7 +5779,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -5829,7 +5796,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -5846,7 +5813,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -5863,7 +5830,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -5880,7 +5847,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -5897,7 +5864,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -5914,7 +5881,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -5931,7 +5898,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -5948,7 +5915,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -5965,7 +5932,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -5982,7 +5949,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -5999,7 +5966,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6016,7 +5983,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6033,7 +6000,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6050,7 +6017,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6067,7 +6034,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6084,7 +6051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6098,7 +6065,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6115,7 +6082,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6132,7 +6099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6149,7 +6116,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -6166,7 +6133,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -6183,7 +6150,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -6200,7 +6167,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -6217,7 +6184,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -6231,7 +6198,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -6248,7 +6215,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -6265,7 +6232,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -6282,7 +6249,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -6296,7 +6263,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -6313,7 +6280,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -6330,7 +6297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -6344,7 +6311,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -6358,7 +6325,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -6375,7 +6342,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -6392,7 +6359,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -6409,7 +6376,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -6423,7 +6390,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -6440,7 +6407,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -6457,7 +6424,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -6474,7 +6441,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -6491,7 +6458,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -6508,7 +6475,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -6525,7 +6492,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -6542,7 +6509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -6559,7 +6526,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -6576,7 +6543,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -6593,7 +6560,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -6610,7 +6577,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -6627,7 +6594,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -6641,7 +6608,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -6658,7 +6625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -6672,7 +6639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -6689,7 +6656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -6706,7 +6673,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -6723,7 +6690,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -6737,7 +6704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -6751,7 +6718,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -6768,7 +6735,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -6782,7 +6749,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -6799,7 +6766,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -6816,7 +6783,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -6830,7 +6797,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -6844,7 +6811,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6858,7 +6825,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6872,7 +6839,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6886,7 +6853,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6903,7 +6870,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6920,7 +6887,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6937,7 +6904,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6951,7 +6918,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6968,7 +6935,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6985,7 +6952,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -7002,7 +6969,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -7019,7 +6986,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -7033,7 +7000,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -7047,7 +7014,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -7061,7 +7028,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -7075,7 +7042,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -7092,7 +7059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -7109,7 +7076,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -7126,7 +7093,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -7143,7 +7110,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -7160,7 +7127,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -7177,7 +7144,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -7194,7 +7161,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -7208,7 +7175,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -7225,7 +7192,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -7239,7 +7206,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -7256,7 +7223,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -7273,7 +7240,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -7290,7 +7257,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -7307,7 +7274,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -7324,7 +7291,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -7341,7 +7308,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -7355,7 +7322,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -7372,7 +7339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -7389,7 +7356,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -7406,7 +7373,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7423,7 +7390,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7437,7 +7404,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7451,7 +7418,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7468,7 +7435,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7485,7 +7452,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7502,7 +7469,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7519,7 +7486,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7536,7 +7503,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7553,7 +7520,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7570,7 +7537,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7587,7 +7554,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7604,7 +7571,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7621,7 +7588,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7638,7 +7605,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7652,7 +7619,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7666,7 +7633,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7680,7 +7647,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7697,7 +7664,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7711,7 +7678,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7725,7 +7692,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7739,7 +7706,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -7753,7 +7720,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -7767,7 +7734,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -7781,7 +7748,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -7798,7 +7765,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -7815,7 +7782,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -7829,7 +7796,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -7846,7 +7813,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -7863,7 +7830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -7877,7 +7844,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -7894,7 +7861,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -7911,7 +7878,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -7928,7 +7895,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -7945,7 +7912,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -7959,7 +7926,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -7976,7 +7943,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -7990,7 +7957,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8007,7 +7974,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8021,7 +7988,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8038,7 +8005,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8055,7 +8022,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8072,7 +8039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8086,7 +8053,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8103,7 +8070,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8120,7 +8087,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8134,7 +8101,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8148,7 +8115,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8165,7 +8132,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8182,7 +8149,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8199,7 +8166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8213,7 +8180,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8230,7 +8197,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8247,7 +8214,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8264,7 +8231,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8281,7 +8248,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8298,7 +8265,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -8315,7 +8282,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -8332,7 +8299,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -8349,7 +8316,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -8366,7 +8333,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -8383,7 +8350,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -8397,7 +8364,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -8414,7 +8381,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -8428,7 +8395,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -8445,7 +8412,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -8459,7 +8426,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -8473,7 +8440,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -8490,7 +8457,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -8507,7 +8474,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -8521,7 +8488,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -8538,7 +8505,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -8555,7 +8522,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -8572,7 +8539,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -8589,7 +8556,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -8606,7 +8573,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -8623,7 +8590,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -8640,7 +8607,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -8657,7 +8624,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -8674,7 +8641,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -8688,7 +8655,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -8702,7 +8669,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -8719,7 +8686,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -8736,7 +8703,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -8750,7 +8717,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -8764,7 +8731,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -8781,7 +8748,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -8795,7 +8762,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -8809,7 +8776,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -8826,7 +8793,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -8840,7 +8807,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -8854,7 +8821,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -8868,7 +8835,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -8882,7 +8849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -8899,7 +8866,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -8913,7 +8880,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -8927,7 +8894,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -8944,7 +8911,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -8958,7 +8925,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -8972,7 +8939,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -8989,7 +8956,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -9003,7 +8970,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -9017,7 +8984,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -9031,7 +8998,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -9045,7 +9012,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -9062,7 +9029,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -9076,7 +9043,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -9093,7 +9060,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -9107,7 +9074,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -9121,7 +9088,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -9135,7 +9102,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -9152,7 +9119,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -9166,7 +9133,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -9183,7 +9150,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -9197,7 +9164,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -9214,7 +9181,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>341</v>
       </c>
@@ -9228,7 +9195,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -9242,7 +9209,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>343</v>
       </c>
@@ -9259,7 +9226,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>344</v>
       </c>
@@ -9273,7 +9240,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>345</v>
       </c>
@@ -9290,7 +9257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -9307,7 +9274,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>347</v>
       </c>
@@ -9321,7 +9288,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -9338,7 +9305,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -9352,7 +9319,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -9366,7 +9333,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>351</v>
       </c>
@@ -9383,7 +9350,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -9400,7 +9367,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>353</v>
       </c>
@@ -9414,7 +9381,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -9428,7 +9395,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>355</v>
       </c>
@@ -9442,7 +9409,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>356</v>
       </c>
@@ -9456,7 +9423,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>357</v>
       </c>
@@ -9473,7 +9440,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -9487,7 +9454,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -9504,7 +9471,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>360</v>
       </c>
@@ -9521,7 +9488,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -9538,7 +9505,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>362</v>
       </c>
@@ -9555,7 +9522,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -9569,7 +9536,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -9586,7 +9553,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -9603,7 +9570,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>366</v>
       </c>
@@ -9620,7 +9587,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -9637,7 +9604,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -9654,7 +9621,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -9671,7 +9638,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -9688,7 +9655,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -9705,7 +9672,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>372</v>
       </c>
@@ -9722,7 +9689,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>373</v>
       </c>
@@ -9739,7 +9706,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>374</v>
       </c>
@@ -9756,7 +9723,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>375</v>
       </c>
@@ -9773,7 +9740,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>376</v>
       </c>
@@ -9790,7 +9757,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>377</v>
       </c>
@@ -9807,7 +9774,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>378</v>
       </c>
@@ -9824,7 +9791,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>379</v>
       </c>
@@ -9841,7 +9808,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -9855,7 +9822,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -9872,7 +9839,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -9886,7 +9853,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -9903,7 +9870,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -9917,7 +9884,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>385</v>
       </c>
@@ -9931,7 +9898,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>386</v>
       </c>
@@ -9948,7 +9915,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>387</v>
       </c>
@@ -9962,7 +9929,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -9976,7 +9943,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -9990,7 +9957,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -10007,7 +9974,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -10024,7 +9991,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -10038,7 +10005,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>393</v>
       </c>
@@ -10052,7 +10019,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -10066,7 +10033,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>395</v>
       </c>
@@ -10080,7 +10047,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -10094,7 +10061,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -10111,7 +10078,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -10125,7 +10092,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -10142,7 +10109,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -10156,7 +10123,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -10173,7 +10140,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>402</v>
       </c>
@@ -10190,7 +10157,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>403</v>
       </c>
@@ -10207,7 +10174,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -10224,7 +10191,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -10238,7 +10205,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -10255,7 +10222,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>407</v>
       </c>
@@ -10272,7 +10239,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -10289,7 +10256,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>409</v>
       </c>
@@ -10303,7 +10270,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>410</v>
       </c>
@@ -10317,7 +10284,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -10334,7 +10301,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>412</v>
       </c>
@@ -10348,7 +10315,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -10362,7 +10329,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -10376,7 +10343,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>415</v>
       </c>
@@ -10390,7 +10357,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -10404,7 +10371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>417</v>
       </c>
@@ -10421,7 +10388,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>418</v>
       </c>
@@ -10435,7 +10402,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>419</v>
       </c>
@@ -10452,7 +10419,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>420</v>
       </c>
@@ -10466,7 +10433,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>421</v>
       </c>
@@ -10480,7 +10447,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>422</v>
       </c>
@@ -10494,7 +10461,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>423</v>
       </c>
@@ -10511,7 +10478,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>424</v>
       </c>
@@ -10525,7 +10492,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>425</v>
       </c>
@@ -10539,7 +10506,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>426</v>
       </c>
@@ -10556,7 +10523,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>427</v>
       </c>
@@ -10570,7 +10537,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>428</v>
       </c>
@@ -10587,7 +10554,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -10604,7 +10571,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>430</v>
       </c>
@@ -10618,7 +10585,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>431</v>
       </c>
@@ -10632,7 +10599,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>432</v>
       </c>
@@ -10649,7 +10616,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>433</v>
       </c>
@@ -10663,7 +10630,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>434</v>
       </c>
@@ -10680,7 +10647,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>435</v>
       </c>
@@ -10694,7 +10661,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>436</v>
       </c>
@@ -10708,7 +10675,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>437</v>
       </c>
@@ -10722,7 +10689,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>438</v>
       </c>
@@ -10736,7 +10703,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>439</v>
       </c>
@@ -10750,7 +10717,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>440</v>
       </c>
@@ -10767,7 +10734,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>441</v>
       </c>
@@ -10784,7 +10751,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>442</v>
       </c>
@@ -10798,7 +10765,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>443</v>
       </c>
@@ -10815,7 +10782,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>444</v>
       </c>
@@ -10832,7 +10799,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>445</v>
       </c>
@@ -10846,7 +10813,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>446</v>
       </c>
@@ -10860,7 +10827,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>447</v>
       </c>
@@ -10874,7 +10841,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>448</v>
       </c>
@@ -10891,7 +10858,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>449</v>
       </c>
@@ -10905,7 +10872,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>450</v>
       </c>
@@ -10919,7 +10886,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>451</v>
       </c>
@@ -10936,7 +10903,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>452</v>
       </c>
@@ -10953,7 +10920,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>453</v>
       </c>
@@ -10970,7 +10937,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>454</v>
       </c>
@@ -10987,7 +10954,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>455</v>
       </c>
@@ -11001,7 +10968,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>456</v>
       </c>
@@ -11018,7 +10985,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>457</v>
       </c>
@@ -11035,7 +11002,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>458</v>
       </c>
@@ -11052,7 +11019,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>459</v>
       </c>
@@ -11069,7 +11036,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>460</v>
       </c>
@@ -11083,7 +11050,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>461</v>
       </c>
@@ -11100,7 +11067,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>462</v>
       </c>
@@ -11117,7 +11084,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>463</v>
       </c>
@@ -11134,7 +11101,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>464</v>
       </c>
@@ -11151,7 +11118,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>465</v>
       </c>
@@ -11165,7 +11132,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>466</v>
       </c>
@@ -11182,7 +11149,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>467</v>
       </c>
@@ -11199,7 +11166,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>468</v>
       </c>
@@ -11216,7 +11183,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>469</v>
       </c>
@@ -11230,7 +11197,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>470</v>
       </c>
@@ -11244,7 +11211,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>471</v>
       </c>
@@ -11258,7 +11225,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>472</v>
       </c>
@@ -11275,7 +11242,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>473</v>
       </c>
@@ -11292,7 +11259,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -11309,7 +11276,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>475</v>
       </c>
@@ -11326,7 +11293,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>476</v>
       </c>
@@ -11343,7 +11310,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>477</v>
       </c>
@@ -11360,7 +11327,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>478</v>
       </c>
@@ -11377,7 +11344,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>479</v>
       </c>
@@ -11394,7 +11361,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>480</v>
       </c>
@@ -11411,7 +11378,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>481</v>
       </c>
@@ -11428,7 +11395,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>482</v>
       </c>
@@ -11442,7 +11409,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>483</v>
       </c>
@@ -11456,7 +11423,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>484</v>
       </c>
@@ -11470,7 +11437,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>485</v>
       </c>
@@ -11484,7 +11451,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>486</v>
       </c>
@@ -11501,7 +11468,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>487</v>
       </c>
@@ -11515,7 +11482,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>488</v>
       </c>
@@ -11529,7 +11496,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>489</v>
       </c>
@@ -11546,7 +11513,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>490</v>
       </c>
@@ -11560,7 +11527,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>491</v>
       </c>
@@ -11574,7 +11541,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>492</v>
       </c>
@@ -11588,7 +11555,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>493</v>
       </c>
@@ -11605,7 +11572,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>494</v>
       </c>
@@ -11619,7 +11586,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>495</v>
       </c>
@@ -11636,7 +11603,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>496</v>
       </c>
@@ -11650,7 +11617,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>497</v>
       </c>
@@ -11667,7 +11634,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>498</v>
       </c>
@@ -11684,7 +11651,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>499</v>
       </c>
@@ -11698,7 +11665,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>500</v>
       </c>
@@ -11712,7 +11679,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>501</v>
       </c>
@@ -11726,7 +11693,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>502</v>
       </c>
@@ -11743,7 +11710,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>503</v>
       </c>
@@ -11760,7 +11727,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>504</v>
       </c>
@@ -11777,7 +11744,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>505</v>
       </c>
@@ -11794,7 +11761,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>506</v>
       </c>
@@ -11811,7 +11778,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>507</v>
       </c>
@@ -11825,7 +11792,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>508</v>
       </c>
@@ -11842,7 +11809,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>509</v>
       </c>
@@ -11856,7 +11823,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>510</v>
       </c>
@@ -11873,7 +11840,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>511</v>
       </c>
@@ -11890,7 +11857,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>512</v>
       </c>
@@ -11907,7 +11874,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>513</v>
       </c>
@@ -11924,7 +11891,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>514</v>
       </c>
@@ -11941,7 +11908,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>515</v>
       </c>
@@ -11955,7 +11922,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>516</v>
       </c>
@@ -11969,7 +11936,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>517</v>
       </c>
@@ -11983,7 +11950,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>518</v>
       </c>
@@ -12000,7 +11967,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>519</v>
       </c>
@@ -12014,7 +11981,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>520</v>
       </c>
@@ -12028,7 +11995,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>521</v>
       </c>
@@ -12042,7 +12009,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>522</v>
       </c>
@@ -12059,7 +12026,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>523</v>
       </c>
@@ -12076,7 +12043,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>524</v>
       </c>
@@ -12090,7 +12057,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>525</v>
       </c>
@@ -12107,7 +12074,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>526</v>
       </c>
@@ -12124,7 +12091,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>527</v>
       </c>
@@ -12141,7 +12108,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>528</v>
       </c>
@@ -12155,7 +12122,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>529</v>
       </c>
@@ -12172,7 +12139,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>530</v>
       </c>
@@ -12186,7 +12153,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>531</v>
       </c>
@@ -12203,7 +12170,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>532</v>
       </c>
@@ -12220,7 +12187,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>533</v>
       </c>
@@ -12234,7 +12201,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>534</v>
       </c>
@@ -12251,7 +12218,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>535</v>
       </c>
@@ -12268,7 +12235,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>536</v>
       </c>
@@ -12282,7 +12249,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>537</v>
       </c>
@@ -12299,7 +12266,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>538</v>
       </c>
@@ -12313,7 +12280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>539</v>
       </c>
@@ -12330,7 +12297,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>540</v>
       </c>
@@ -12344,7 +12311,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>541</v>
       </c>
@@ -12361,7 +12328,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>542</v>
       </c>
@@ -12375,7 +12342,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>543</v>
       </c>
@@ -12389,7 +12356,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>544</v>
       </c>
@@ -12406,7 +12373,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>545</v>
       </c>
@@ -12423,7 +12390,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>546</v>
       </c>
@@ -12437,7 +12404,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>547</v>
       </c>
@@ -12451,7 +12418,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>548</v>
       </c>
@@ -12465,7 +12432,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>549</v>
       </c>
@@ -12479,7 +12446,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>550</v>
       </c>
@@ -12493,7 +12460,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>551</v>
       </c>
@@ -12507,7 +12474,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>552</v>
       </c>
@@ -12521,7 +12488,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>553</v>
       </c>
@@ -12538,7 +12505,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>554</v>
       </c>
@@ -12555,7 +12522,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>555</v>
       </c>
@@ -12572,7 +12539,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>556</v>
       </c>
@@ -12586,7 +12553,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>557</v>
       </c>
@@ -12603,7 +12570,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>558</v>
       </c>
@@ -12617,7 +12584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>559</v>
       </c>
@@ -12631,7 +12598,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>560</v>
       </c>
@@ -12645,7 +12612,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>561</v>
       </c>
@@ -12662,7 +12629,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>562</v>
       </c>
@@ -12679,7 +12646,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>563</v>
       </c>
@@ -12696,7 +12663,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>564</v>
       </c>
@@ -12710,7 +12677,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>565</v>
       </c>
@@ -12727,7 +12694,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>566</v>
       </c>
@@ -12741,7 +12708,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>567</v>
       </c>
@@ -12758,7 +12725,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>568</v>
       </c>
@@ -12775,7 +12742,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>569</v>
       </c>
@@ -12789,7 +12756,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>570</v>
       </c>
@@ -12806,7 +12773,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>571</v>
       </c>
@@ -12820,7 +12787,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>572</v>
       </c>
@@ -12837,7 +12804,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>573</v>
       </c>
@@ -12851,7 +12818,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>574</v>
       </c>
@@ -12868,7 +12835,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>575</v>
       </c>
@@ -12885,7 +12852,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>576</v>
       </c>
@@ -12899,7 +12866,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>577</v>
       </c>
@@ -12913,7 +12880,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>578</v>
       </c>
@@ -12930,7 +12897,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>579</v>
       </c>
@@ -12947,7 +12914,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>580</v>
       </c>
@@ -12964,7 +12931,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>581</v>
       </c>
@@ -12978,7 +12945,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>582</v>
       </c>
@@ -12992,7 +12959,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>583</v>
       </c>
@@ -13009,7 +12976,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>584</v>
       </c>
@@ -13023,7 +12990,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>585</v>
       </c>
@@ -13040,7 +13007,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>586</v>
       </c>
@@ -13057,7 +13024,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>587</v>
       </c>
@@ -13074,7 +13041,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>588</v>
       </c>
@@ -13091,7 +13058,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>589</v>
       </c>
@@ -13105,7 +13072,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>590</v>
       </c>
@@ -13119,7 +13086,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>591</v>
       </c>
@@ -13136,7 +13103,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>592</v>
       </c>
@@ -13153,7 +13120,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>593</v>
       </c>
@@ -13167,7 +13134,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>594</v>
       </c>
@@ -13184,7 +13151,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>595</v>
       </c>
@@ -13201,7 +13168,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>596</v>
       </c>
@@ -13218,7 +13185,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>597</v>
       </c>
@@ -13235,7 +13202,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>598</v>
       </c>
@@ -13252,7 +13219,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>599</v>
       </c>
@@ -13269,7 +13236,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>600</v>
       </c>
@@ -13283,7 +13250,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>601</v>
       </c>
@@ -13297,7 +13264,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>602</v>
       </c>
@@ -13311,7 +13278,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>603</v>
       </c>
@@ -13328,7 +13295,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>604</v>
       </c>
@@ -13345,7 +13312,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>605</v>
       </c>
@@ -13362,7 +13329,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>606</v>
       </c>
@@ -13376,7 +13343,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>607</v>
       </c>
@@ -13393,7 +13360,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>608</v>
       </c>
@@ -13407,7 +13374,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>609</v>
       </c>
@@ -13421,7 +13388,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>610</v>
       </c>
@@ -13435,7 +13402,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>611</v>
       </c>
@@ -13452,7 +13419,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>612</v>
       </c>
@@ -13466,7 +13433,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>613</v>
       </c>
@@ -13480,7 +13447,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>614</v>
       </c>
@@ -13494,7 +13461,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>615</v>
       </c>
@@ -13511,7 +13478,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>616</v>
       </c>
@@ -13528,7 +13495,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>617</v>
       </c>
@@ -13542,7 +13509,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>618</v>
       </c>
@@ -13559,7 +13526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>619</v>
       </c>
@@ -13576,7 +13543,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>620</v>
       </c>
@@ -13593,7 +13560,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>621</v>
       </c>
@@ -13610,7 +13577,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>622</v>
       </c>
@@ -13624,7 +13591,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>623</v>
       </c>
@@ -13638,7 +13605,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>624</v>
       </c>
@@ -13652,7 +13619,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>625</v>
       </c>
@@ -13669,7 +13636,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>626</v>
       </c>
@@ -13683,7 +13650,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>627</v>
       </c>
@@ -13700,7 +13667,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>628</v>
       </c>
@@ -13714,7 +13681,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>629</v>
       </c>
@@ -13728,7 +13695,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>630</v>
       </c>
@@ -13745,7 +13712,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>631</v>
       </c>
@@ -13762,7 +13729,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>632</v>
       </c>
@@ -13779,7 +13746,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>633</v>
       </c>
@@ -13796,7 +13763,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>634</v>
       </c>
@@ -13813,7 +13780,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>635</v>
       </c>
@@ -13830,7 +13797,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>636</v>
       </c>
@@ -13844,7 +13811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>637</v>
       </c>
@@ -13861,7 +13828,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>638</v>
       </c>
@@ -13875,7 +13842,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>639</v>
       </c>
@@ -13889,7 +13856,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>640</v>
       </c>
@@ -13906,7 +13873,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>641</v>
       </c>
@@ -13923,7 +13890,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>642</v>
       </c>
@@ -13937,7 +13904,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>643</v>
       </c>
@@ -13954,7 +13921,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>644</v>
       </c>
@@ -13968,7 +13935,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>645</v>
       </c>
@@ -13982,7 +13949,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>646</v>
       </c>
@@ -13996,7 +13963,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>647</v>
       </c>
@@ -14013,7 +13980,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>648</v>
       </c>
@@ -14027,7 +13994,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>649</v>
       </c>
@@ -14041,7 +14008,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>650</v>
       </c>
@@ -14058,7 +14025,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>651</v>
       </c>
@@ -14075,7 +14042,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>652</v>
       </c>
@@ -14089,7 +14056,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>653</v>
       </c>
@@ -14103,7 +14070,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>654</v>
       </c>
@@ -14120,7 +14087,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>655</v>
       </c>
@@ -14137,7 +14104,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>656</v>
       </c>
@@ -14151,7 +14118,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>657</v>
       </c>
@@ -14165,7 +14132,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>658</v>
       </c>
@@ -14182,7 +14149,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>659</v>
       </c>
@@ -14196,7 +14163,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>660</v>
       </c>
@@ -14210,7 +14177,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>661</v>
       </c>
@@ -14224,7 +14191,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>662</v>
       </c>
@@ -14238,7 +14205,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>663</v>
       </c>
@@ -14252,7 +14219,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>664</v>
       </c>
@@ -14266,7 +14233,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>665</v>
       </c>
@@ -14283,7 +14250,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>666</v>
       </c>
@@ -14297,7 +14264,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>667</v>
       </c>
@@ -14311,7 +14278,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>668</v>
       </c>
@@ -14325,7 +14292,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>669</v>
       </c>
@@ -14342,7 +14309,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>670</v>
       </c>
@@ -14356,7 +14323,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>671</v>
       </c>
@@ -14370,7 +14337,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>672</v>
       </c>
@@ -14384,7 +14351,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>673</v>
       </c>
@@ -14398,7 +14365,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>674</v>
       </c>
@@ -14415,7 +14382,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>675</v>
       </c>
@@ -14429,7 +14396,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>676</v>
       </c>
@@ -14446,7 +14413,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>677</v>
       </c>
@@ -14460,7 +14427,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>678</v>
       </c>
@@ -14474,7 +14441,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>679</v>
       </c>
@@ -14488,7 +14455,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>680</v>
       </c>
@@ -14502,7 +14469,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>681</v>
       </c>
@@ -14516,7 +14483,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>682</v>
       </c>
@@ -14530,7 +14497,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>683</v>
       </c>
@@ -14544,7 +14511,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>684</v>
       </c>
@@ -14558,7 +14525,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>685</v>
       </c>
@@ -14575,7 +14542,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>686</v>
       </c>
@@ -14589,7 +14556,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>687</v>
       </c>
@@ -14606,7 +14573,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>688</v>
       </c>
@@ -14620,7 +14587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>689</v>
       </c>
@@ -14637,7 +14604,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>690</v>
       </c>
@@ -14654,7 +14621,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>691</v>
       </c>
@@ -14668,7 +14635,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>692</v>
       </c>
@@ -14685,7 +14652,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>693</v>
       </c>
@@ -14699,7 +14666,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>694</v>
       </c>
@@ -14713,7 +14680,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>695</v>
       </c>
@@ -14730,7 +14697,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>696</v>
       </c>
@@ -14744,7 +14711,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>697</v>
       </c>
@@ -14758,7 +14725,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>698</v>
       </c>
@@ -14775,7 +14742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>699</v>
       </c>
@@ -14789,7 +14756,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>700</v>
       </c>
@@ -14803,7 +14770,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>701</v>
       </c>
